--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Implantable Device: Prosthesis, ResourceType Device</t>
+    <t>This StructureDefinition contains the maps for VistA PROSTHESIS INSTALLED (file 130.01) to FHIR Device</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="454">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-implantable-device</t>
+    <t>http://va.gov/fhir/StructureDefinition/ImplantableDeviceDevice</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -627,6 +627,9 @@
   </si>
   <si>
     <t>The device identifier (DI), a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+  </si>
+  <si>
+    <t>1353: target not supported</t>
   </si>
   <si>
     <t>Device.udiCarrier.issuer</t>
@@ -766,6 +769,9 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>1355: target not supported</t>
+  </si>
+  <si>
     <t>Device.statusReason</t>
   </si>
   <si>
@@ -803,6 +809,9 @@
     <t>The lot or batch number within which a device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.</t>
   </si>
   <si>
+    <t>1363: target not supported</t>
+  </si>
+  <si>
     <t>Device.manufacturer</t>
   </si>
   <si>
@@ -840,6 +849,9 @@
     <t>The date a specific device was manufactured - which is a component of the production identifier (PI), a conditional, variable portion of a UDI.  For FHIR, The datetime syntax must converted to YYYY-MM-DD[THH:MM:SS].  If hour is present, the minutes and seconds should both be set to “00”.</t>
   </si>
   <si>
+    <t>1371: target not supported</t>
+  </si>
+  <si>
     <t>Device.expirationDate</t>
   </si>
   <si>
@@ -904,6 +916,9 @@
   </si>
   <si>
     <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
+  </si>
+  <si>
+    <t>1386: target not supported</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -4610,19 +4625,19 @@
         <v>37</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>37</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4644,10 +4659,10 @@
         <v>59</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4698,7 +4713,7 @@
         <v>37</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
@@ -4713,13 +4728,13 @@
         <v>57</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>37</v>
@@ -4730,10 +4745,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4759,14 +4774,14 @@
         <v>59</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>37</v>
@@ -4815,7 +4830,7 @@
         <v>37</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
@@ -4830,7 +4845,7 @@
         <v>57</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>37</v>
@@ -4847,14 +4862,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4873,16 +4888,16 @@
         <v>46</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4932,7 +4947,7 @@
         <v>37</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
@@ -4953,7 +4968,7 @@
         <v>37</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>37</v>
@@ -4964,14 +4979,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4993,13 +5008,13 @@
         <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5049,7 +5064,7 @@
         <v>37</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>38</v>
@@ -5070,7 +5085,7 @@
         <v>37</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>37</v>
@@ -5081,10 +5096,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5110,14 +5125,14 @@
         <v>65</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>37</v>
@@ -5145,10 +5160,10 @@
         <v>127</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>37</v>
@@ -5166,7 +5181,7 @@
         <v>37</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -5181,7 +5196,7 @@
         <v>57</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>37</v>
@@ -5198,10 +5213,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5227,13 +5242,13 @@
         <v>65</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5262,10 +5277,10 @@
         <v>127</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>37</v>
@@ -5283,7 +5298,7 @@
         <v>37</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>38</v>
@@ -5298,10 +5313,10 @@
         <v>57</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>37</v>
@@ -5310,15 +5325,15 @@
         <v>37</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>37</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5344,10 +5359,10 @@
         <v>133</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5377,10 +5392,10 @@
         <v>138</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>37</v>
@@ -5398,7 +5413,7 @@
         <v>37</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
@@ -5416,7 +5431,7 @@
         <v>37</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>37</v>
@@ -5430,14 +5445,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5459,13 +5474,13 @@
         <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5515,7 +5530,7 @@
         <v>37</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
@@ -5530,27 +5545,27 @@
         <v>57</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>37</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5576,10 +5591,10 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5630,7 +5645,7 @@
         <v>37</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
@@ -5645,7 +5660,7 @@
         <v>57</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>193</v>
@@ -5654,18 +5669,18 @@
         <v>88</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5688,13 +5703,13 @@
         <v>37</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5745,7 +5760,7 @@
         <v>37</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>38</v>
@@ -5760,27 +5775,27 @@
         <v>57</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>37</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5803,13 +5818,13 @@
         <v>37</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5860,7 +5875,7 @@
         <v>37</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>38</v>
@@ -5875,27 +5890,27 @@
         <v>57</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5921,10 +5936,10 @@
         <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5975,7 +5990,7 @@
         <v>37</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
@@ -5990,27 +6005,27 @@
         <v>57</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>193</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6036,13 +6051,13 @@
         <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6092,7 +6107,7 @@
         <v>37</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
@@ -6107,7 +6122,7 @@
         <v>57</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>193</v>
@@ -6116,18 +6131,18 @@
         <v>37</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6153,10 +6168,10 @@
         <v>176</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6207,7 +6222,7 @@
         <v>37</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>38</v>
@@ -6234,15 +6249,15 @@
         <v>37</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>37</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6354,10 +6369,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6471,10 +6486,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6590,14 +6605,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6619,10 +6634,10 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6673,7 +6688,7 @@
         <v>37</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>45</v>
@@ -6697,18 +6712,18 @@
         <v>37</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6734,10 +6749,10 @@
         <v>65</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6767,10 +6782,10 @@
         <v>127</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>37</v>
@@ -6788,7 +6803,7 @@
         <v>37</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>45</v>
@@ -6803,7 +6818,7 @@
         <v>57</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>193</v>
@@ -6820,10 +6835,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6849,10 +6864,10 @@
         <v>111</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6903,7 +6918,7 @@
         <v>37</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
@@ -6918,7 +6933,7 @@
         <v>57</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>193</v>
@@ -6927,18 +6942,18 @@
         <v>37</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6964,13 +6979,13 @@
         <v>111</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7020,7 +7035,7 @@
         <v>37</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
@@ -7035,7 +7050,7 @@
         <v>57</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>193</v>
@@ -7052,10 +7067,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7081,10 +7096,10 @@
         <v>133</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7114,10 +7129,10 @@
         <v>138</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>37</v>
@@ -7135,7 +7150,7 @@
         <v>37</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
@@ -7167,10 +7182,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7282,10 +7297,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7399,10 +7414,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7425,19 +7440,19 @@
         <v>46</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>37</v>
@@ -7486,7 +7501,7 @@
         <v>37</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>38</v>
@@ -7501,7 +7516,7 @@
         <v>57</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>37</v>
@@ -7518,10 +7533,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7633,10 +7648,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7750,10 +7765,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7779,16 +7794,16 @@
         <v>59</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>37</v>
@@ -7837,7 +7852,7 @@
         <v>37</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>38</v>
@@ -7852,7 +7867,7 @@
         <v>57</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>37</v>
@@ -7869,10 +7884,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7898,13 +7913,13 @@
         <v>111</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7954,7 +7969,7 @@
         <v>37</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>38</v>
@@ -7969,7 +7984,7 @@
         <v>57</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>37</v>
@@ -7986,10 +8001,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8015,14 +8030,14 @@
         <v>65</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>37</v>
@@ -8071,7 +8086,7 @@
         <v>37</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>38</v>
@@ -8086,7 +8101,7 @@
         <v>57</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>37</v>
@@ -8098,15 +8113,15 @@
         <v>37</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8132,14 +8147,14 @@
         <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>37</v>
@@ -8188,7 +8203,7 @@
         <v>37</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>38</v>
@@ -8203,7 +8218,7 @@
         <v>57</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>37</v>
@@ -8220,10 +8235,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8246,19 +8261,19 @@
         <v>46</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>37</v>
@@ -8307,7 +8322,7 @@
         <v>37</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>38</v>
@@ -8322,7 +8337,7 @@
         <v>57</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>37</v>
@@ -8339,10 +8354,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8368,16 +8383,16 @@
         <v>111</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>37</v>
@@ -8426,7 +8441,7 @@
         <v>37</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>38</v>
@@ -8441,7 +8456,7 @@
         <v>57</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>37</v>
@@ -8458,10 +8473,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8487,10 +8502,10 @@
         <v>176</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8541,7 +8556,7 @@
         <v>37</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>38</v>
@@ -8573,10 +8588,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8688,10 +8703,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8805,10 +8820,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8924,14 +8939,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8953,10 +8968,10 @@
         <v>133</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9007,7 +9022,7 @@
         <v>37</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>45</v>
@@ -9039,10 +9054,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9068,10 +9083,10 @@
         <v>111</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9122,7 +9137,7 @@
         <v>37</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>38</v>
@@ -9154,10 +9169,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9183,10 +9198,10 @@
         <v>176</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9237,7 +9252,7 @@
         <v>37</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>38</v>
@@ -9269,10 +9284,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9384,10 +9399,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9501,10 +9516,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9620,14 +9635,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9649,10 +9664,10 @@
         <v>133</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9703,7 +9718,7 @@
         <v>37</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>38</v>
@@ -9735,10 +9750,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9764,10 +9779,10 @@
         <v>103</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9818,7 +9833,7 @@
         <v>37</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>38</v>
@@ -9850,10 +9865,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9879,10 +9894,10 @@
         <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9933,7 +9948,7 @@
         <v>37</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>45</v>
@@ -9965,10 +9980,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9994,10 +10009,10 @@
         <v>176</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10048,7 +10063,7 @@
         <v>37</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>38</v>
@@ -10080,10 +10095,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10195,10 +10210,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10312,10 +10327,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10431,10 +10446,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10460,10 +10475,10 @@
         <v>133</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10514,7 +10529,7 @@
         <v>37</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>45</v>
@@ -10546,10 +10561,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10572,13 +10587,13 @@
         <v>37</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10629,7 +10644,7 @@
         <v>37</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>38</v>
@@ -10661,10 +10676,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10690,10 +10705,10 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10744,7 +10759,7 @@
         <v>37</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>38</v>
@@ -10776,10 +10791,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10802,17 +10817,17 @@
         <v>37</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>37</v>
@@ -10861,7 +10876,7 @@
         <v>37</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>38</v>
@@ -10876,27 +10891,27 @@
         <v>57</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>37</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10922,10 +10937,10 @@
         <v>165</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10976,7 +10991,7 @@
         <v>37</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>38</v>
@@ -10991,10 +11006,10 @@
         <v>57</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>37</v>
@@ -11008,10 +11023,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11034,16 +11049,16 @@
         <v>37</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11093,7 +11108,7 @@
         <v>37</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>38</v>
@@ -11108,10 +11123,10 @@
         <v>57</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>37</v>
@@ -11125,10 +11140,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11151,17 +11166,17 @@
         <v>37</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>37</v>
@@ -11210,7 +11225,7 @@
         <v>37</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>38</v>
@@ -11225,10 +11240,10 @@
         <v>57</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>37</v>
@@ -11242,10 +11257,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11271,13 +11286,13 @@
         <v>59</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11327,7 +11342,7 @@
         <v>37</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>38</v>
@@ -11342,10 +11357,10 @@
         <v>57</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL82" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>37</v>
@@ -11359,10 +11374,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11385,13 +11400,13 @@
         <v>37</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11442,7 +11457,7 @@
         <v>37</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>38</v>
@@ -11457,7 +11472,7 @@
         <v>57</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>37</v>
@@ -11474,10 +11489,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11503,10 +11518,10 @@
         <v>133</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11557,7 +11572,7 @@
         <v>37</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>38</v>
@@ -11572,7 +11587,7 @@
         <v>57</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>37</v>
@@ -11589,10 +11604,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11615,13 +11630,13 @@
         <v>37</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11672,7 +11687,7 @@
         <v>37</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>38</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="496">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1222,6 +1222,10 @@
   </si>
   <si>
     <t>Coding.code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-7:1393: fixed value "63653004" {null}</t>
   </si>
   <si>
     <t>./code</t>
@@ -8347,10 +8351,10 @@
         <v>78</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>98</v>
+        <v>385</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>78</v>
@@ -8362,15 +8366,15 @@
         <v>78</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8396,14 +8400,14 @@
         <v>152</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8452,7 +8456,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8467,7 +8471,7 @@
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>78</v>
@@ -8484,10 +8488,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8510,19 +8514,19 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8571,7 +8575,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8586,7 +8590,7 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>78</v>
@@ -8603,10 +8607,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8632,16 +8636,16 @@
         <v>152</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -8690,7 +8694,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8705,7 +8709,7 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>78</v>
@@ -8722,10 +8726,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8751,10 +8755,10 @@
         <v>217</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8805,7 +8809,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8837,10 +8841,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8952,10 +8956,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9069,10 +9073,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9188,10 +9192,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9217,10 +9221,10 @@
         <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9271,7 +9275,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>86</v>
@@ -9303,10 +9307,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9332,10 +9336,10 @@
         <v>152</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9386,7 +9390,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9418,10 +9422,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9447,10 +9451,10 @@
         <v>217</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9501,7 +9505,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9533,10 +9537,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9648,10 +9652,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9765,10 +9769,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9884,10 +9888,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9913,10 +9917,10 @@
         <v>174</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9967,7 +9971,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9999,10 +10003,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10028,10 +10032,10 @@
         <v>144</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10082,7 +10086,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10114,10 +10118,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10143,10 +10147,10 @@
         <v>152</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10197,7 +10201,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>86</v>
@@ -10229,10 +10233,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10258,10 +10262,10 @@
         <v>217</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10312,7 +10316,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10344,10 +10348,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10459,10 +10463,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10576,10 +10580,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10695,10 +10699,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10724,10 +10728,10 @@
         <v>174</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10778,7 +10782,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>86</v>
@@ -10810,10 +10814,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10836,13 +10840,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10893,7 +10897,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10925,10 +10929,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10954,10 +10958,10 @@
         <v>174</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11008,7 +11012,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11040,10 +11044,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11066,17 +11070,17 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11125,7 +11129,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11140,27 +11144,27 @@
         <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11186,10 +11190,10 @@
         <v>206</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11240,7 +11244,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11255,10 +11259,10 @@
         <v>98</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11272,10 +11276,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11298,16 +11302,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11357,7 +11361,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11372,10 +11376,10 @@
         <v>98</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11389,10 +11393,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11415,17 +11419,17 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11474,7 +11478,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11489,10 +11493,10 @@
         <v>98</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11506,10 +11510,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11535,13 +11539,13 @@
         <v>100</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11591,7 +11595,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11606,10 +11610,10 @@
         <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11623,10 +11627,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11649,13 +11653,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11706,7 +11710,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11721,7 +11725,7 @@
         <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>78</v>
@@ -11738,10 +11742,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11767,10 +11771,10 @@
         <v>174</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11821,7 +11825,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -11853,10 +11857,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11879,13 +11883,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -11936,7 +11940,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1225,7 +1225,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-7:1393: fixed value "63653004" {null}</t>
+inv-8:1393: fixed value = 63653004 {null}</t>
   </si>
   <si>
     <t>./code</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1225,7 +1225,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-8:1393: fixed value = 63653004 {null}</t>
+inv-9:1393: fixed value = 63653004 {null}</t>
   </si>
   <si>
     <t>./code</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
+++ b/docs/StructureDefinition-ImplantableDeviceProsthesisDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA PROSTHESIS INSTALLED (file 130.01) to FHIR Device</t>
+    <t>This StructureDefinition contains the maps for VistA file PROSTHESIS INSTALLED (#130.01) to ImplantableDeviceDevice</t>
   </si>
   <si>
     <t>Purpose</t>
